--- a/data/input/market.xlsx
+++ b/data/input/market.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F302"/>
+  <dimension ref="A1:F303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4425,7 +4425,7 @@
         <v>1870.36</v>
       </c>
       <c r="F198" t="n">
-        <v>1030969130</v>
+        <v>953432252</v>
       </c>
     </row>
     <row r="199">
@@ -4445,7 +4445,7 @@
         <v>1853.29</v>
       </c>
       <c r="F199" t="n">
-        <v>673852010</v>
+        <v>568682199</v>
       </c>
     </row>
     <row r="200">
@@ -4485,7 +4485,7 @@
         <v>1875.84</v>
       </c>
       <c r="F201" t="n">
-        <v>629723569</v>
+        <v>577907915</v>
       </c>
     </row>
     <row r="202">
@@ -4499,13 +4499,13 @@
         <v>1881.18</v>
       </c>
       <c r="D202" t="n">
-        <v>1840.58</v>
+        <v>1852.49</v>
       </c>
       <c r="E202" t="n">
         <v>1854.1</v>
       </c>
       <c r="F202" t="n">
-        <v>722302348</v>
+        <v>626247808</v>
       </c>
     </row>
     <row r="203">
@@ -4565,7 +4565,7 @@
         <v>1854.06</v>
       </c>
       <c r="F205" t="n">
-        <v>692675996</v>
+        <v>614072346</v>
       </c>
     </row>
     <row r="206">
@@ -4585,7 +4585,7 @@
         <v>1874.85</v>
       </c>
       <c r="F206" t="n">
-        <v>773453598</v>
+        <v>701963400</v>
       </c>
     </row>
     <row r="207">
@@ -4605,7 +4605,7 @@
         <v>1891.2</v>
       </c>
       <c r="F207" t="n">
-        <v>875178670</v>
+        <v>788372585</v>
       </c>
     </row>
     <row r="208">
@@ -4619,13 +4619,13 @@
         <v>1924.95</v>
       </c>
       <c r="D208" t="n">
-        <v>1896.45</v>
+        <v>1891.2</v>
       </c>
       <c r="E208" t="n">
         <v>1909.01</v>
       </c>
       <c r="F208" t="n">
-        <v>961003323</v>
+        <v>852195767</v>
       </c>
     </row>
     <row r="209">
@@ -4645,7 +4645,7 @@
         <v>1915.37</v>
       </c>
       <c r="F209" t="n">
-        <v>944197112</v>
+        <v>840759266</v>
       </c>
     </row>
     <row r="210">
@@ -4659,13 +4659,13 @@
         <v>1927.06</v>
       </c>
       <c r="D210" t="n">
-        <v>1892.1</v>
+        <v>1893.75</v>
       </c>
       <c r="E210" t="n">
         <v>1895.5</v>
       </c>
       <c r="F210" t="n">
-        <v>960671699</v>
+        <v>870568077</v>
       </c>
     </row>
     <row r="211">
@@ -4679,13 +4679,13 @@
         <v>1906.64</v>
       </c>
       <c r="D211" t="n">
-        <v>1871.44</v>
+        <v>1875.25</v>
       </c>
       <c r="E211" t="n">
         <v>1901.1</v>
       </c>
       <c r="F211" t="n">
-        <v>733300648</v>
+        <v>646156258</v>
       </c>
     </row>
     <row r="212">
@@ -4705,7 +4705,7 @@
         <v>1898.37</v>
       </c>
       <c r="F212" t="n">
-        <v>972787205</v>
+        <v>796945943</v>
       </c>
     </row>
     <row r="213">
@@ -4725,7 +4725,7 @@
         <v>1925.46</v>
       </c>
       <c r="F213" t="n">
-        <v>675088585</v>
+        <v>580872676</v>
       </c>
     </row>
     <row r="214">
@@ -4739,13 +4739,13 @@
         <v>1930.58</v>
       </c>
       <c r="D214" t="n">
-        <v>1909.69</v>
+        <v>1909.9</v>
       </c>
       <c r="E214" t="n">
         <v>1921.6</v>
       </c>
       <c r="F214" t="n">
-        <v>744584792</v>
+        <v>708757508</v>
       </c>
     </row>
     <row r="215">
@@ -4765,7 +4765,7 @@
         <v>1927.94</v>
       </c>
       <c r="F215" t="n">
-        <v>820722199</v>
+        <v>774679381</v>
       </c>
     </row>
     <row r="216">
@@ -4779,13 +4779,13 @@
         <v>1933.11</v>
       </c>
       <c r="D216" t="n">
-        <v>1902.87</v>
+        <v>1904.47</v>
       </c>
       <c r="E216" t="n">
         <v>1912.93</v>
       </c>
       <c r="F216" t="n">
-        <v>1007594006</v>
+        <v>904325068</v>
       </c>
     </row>
     <row r="217">
@@ -4805,7 +4805,7 @@
         <v>1913.23</v>
       </c>
       <c r="F217" t="n">
-        <v>1197618071</v>
+        <v>1078815114</v>
       </c>
     </row>
     <row r="218">
@@ -4825,7 +4825,7 @@
         <v>1896.89</v>
       </c>
       <c r="F218" t="n">
-        <v>677251003</v>
+        <v>562755083</v>
       </c>
     </row>
     <row r="219">
@@ -4845,7 +4845,7 @@
         <v>1877.13</v>
       </c>
       <c r="F219" t="n">
-        <v>854173859</v>
+        <v>650651924</v>
       </c>
     </row>
     <row r="220">
@@ -4865,7 +4865,7 @@
         <v>1886.03</v>
       </c>
       <c r="F220" t="n">
-        <v>702575224</v>
+        <v>495245425</v>
       </c>
     </row>
     <row r="221">
@@ -4885,7 +4885,7 @@
         <v>1884.18</v>
       </c>
       <c r="F221" t="n">
-        <v>729758151</v>
+        <v>598836621</v>
       </c>
     </row>
     <row r="222">
@@ -4899,13 +4899,13 @@
         <v>1889.87</v>
       </c>
       <c r="D222" t="n">
-        <v>1861.85</v>
+        <v>1863.18</v>
       </c>
       <c r="E222" t="n">
         <v>1874.43</v>
       </c>
       <c r="F222" t="n">
-        <v>830501943</v>
+        <v>667675136</v>
       </c>
     </row>
     <row r="223">
@@ -4925,7 +4925,7 @@
         <v>1863.67</v>
       </c>
       <c r="F223" t="n">
-        <v>686200721</v>
+        <v>602798527</v>
       </c>
     </row>
     <row r="224">
@@ -4939,13 +4939,13 @@
         <v>1873.17</v>
       </c>
       <c r="D224" t="n">
-        <v>1854.34</v>
+        <v>1855.96</v>
       </c>
       <c r="E224" t="n">
         <v>1863.49</v>
       </c>
       <c r="F224" t="n">
-        <v>688077025</v>
+        <v>556018675</v>
       </c>
     </row>
     <row r="225">
@@ -4959,13 +4959,13 @@
         <v>1871.09</v>
       </c>
       <c r="D225" t="n">
-        <v>1840.4</v>
+        <v>1841.39</v>
       </c>
       <c r="E225" t="n">
         <v>1844.54</v>
       </c>
       <c r="F225" t="n">
-        <v>506972140</v>
+        <v>431817093</v>
       </c>
     </row>
     <row r="226">
@@ -4979,13 +4979,13 @@
         <v>1858.76</v>
       </c>
       <c r="D226" t="n">
-        <v>1822.32</v>
+        <v>1824.08</v>
       </c>
       <c r="E226" t="n">
         <v>1826.47</v>
       </c>
       <c r="F226" t="n">
-        <v>727018675</v>
+        <v>644649712</v>
       </c>
     </row>
     <row r="227">
@@ -5005,7 +5005,7 @@
         <v>1819.01</v>
       </c>
       <c r="F227" t="n">
-        <v>722920164</v>
+        <v>601720451</v>
       </c>
     </row>
     <row r="228">
@@ -5025,7 +5025,7 @@
         <v>1831.55</v>
       </c>
       <c r="F228" t="n">
-        <v>601316050</v>
+        <v>450907795</v>
       </c>
     </row>
     <row r="229">
@@ -5039,13 +5039,13 @@
         <v>1846.71</v>
       </c>
       <c r="D229" t="n">
-        <v>1830.37</v>
+        <v>1831.55</v>
       </c>
       <c r="E229" t="n">
         <v>1838.9</v>
       </c>
       <c r="F229" t="n">
-        <v>502964274</v>
+        <v>444418387</v>
       </c>
     </row>
     <row r="230">
@@ -5056,7 +5056,7 @@
         <v>1822.1</v>
       </c>
       <c r="C230" t="n">
-        <v>1822.95</v>
+        <v>1838.9</v>
       </c>
       <c r="D230" t="n">
         <v>1789.31</v>
@@ -5065,7 +5065,7 @@
         <v>1790.53</v>
       </c>
       <c r="F230" t="n">
-        <v>714568751</v>
+        <v>613416648</v>
       </c>
     </row>
     <row r="231">
@@ -5085,7 +5085,7 @@
         <v>1793.05</v>
       </c>
       <c r="F231" t="n">
-        <v>527110166</v>
+        <v>423962378</v>
       </c>
     </row>
     <row r="232">
@@ -5105,7 +5105,7 @@
         <v>1803.71</v>
       </c>
       <c r="F232" t="n">
-        <v>625012446</v>
+        <v>459074178</v>
       </c>
     </row>
     <row r="233">
@@ -5116,7 +5116,7 @@
         <v>1793.15</v>
       </c>
       <c r="C233" t="n">
-        <v>1801.99</v>
+        <v>1803.71</v>
       </c>
       <c r="D233" t="n">
         <v>1788.64</v>
@@ -5125,7 +5125,7 @@
         <v>1798.61</v>
       </c>
       <c r="F233" t="n">
-        <v>410733903</v>
+        <v>376827746</v>
       </c>
     </row>
     <row r="234">
@@ -5139,13 +5139,13 @@
         <v>1813.57</v>
       </c>
       <c r="D234" t="n">
-        <v>1788.56</v>
+        <v>1788.8</v>
       </c>
       <c r="E234" t="n">
         <v>1791.65</v>
       </c>
       <c r="F234" t="n">
-        <v>640199320</v>
+        <v>577651426</v>
       </c>
     </row>
     <row r="235">
@@ -5165,7 +5165,7 @@
         <v>1799.31</v>
       </c>
       <c r="F235" t="n">
-        <v>792064448</v>
+        <v>620696256</v>
       </c>
     </row>
     <row r="236">
@@ -5179,13 +5179,13 @@
         <v>1811.59</v>
       </c>
       <c r="D236" t="n">
-        <v>1799.86</v>
+        <v>1799.31</v>
       </c>
       <c r="E236" t="n">
         <v>1807.94</v>
       </c>
       <c r="F236" t="n">
-        <v>672837809</v>
+        <v>573796720</v>
       </c>
     </row>
     <row r="237">
@@ -5205,7 +5205,7 @@
         <v>1806.2</v>
       </c>
       <c r="F237" t="n">
-        <v>821620763</v>
+        <v>626382635</v>
       </c>
     </row>
     <row r="238">
@@ -5219,13 +5219,13 @@
         <v>1836.4</v>
       </c>
       <c r="D238" t="n">
-        <v>1819.62</v>
+        <v>1806.2</v>
       </c>
       <c r="E238" t="n">
         <v>1830.47</v>
       </c>
       <c r="F238" t="n">
-        <v>633590659</v>
+        <v>505768931</v>
       </c>
     </row>
     <row r="239">
@@ -5239,13 +5239,13 @@
         <v>1838.52</v>
       </c>
       <c r="D239" t="n">
-        <v>1798.56</v>
+        <v>1822.47</v>
       </c>
       <c r="E239" t="n">
         <v>1824.53</v>
       </c>
       <c r="F239" t="n">
-        <v>608253674</v>
+        <v>526745031</v>
       </c>
     </row>
     <row r="240">
@@ -5265,7 +5265,7 @@
         <v>1857.91</v>
       </c>
       <c r="F240" t="n">
-        <v>517581557</v>
+        <v>443165448</v>
       </c>
     </row>
     <row r="241">
@@ -5279,13 +5279,13 @@
         <v>1886.6</v>
       </c>
       <c r="D241" t="n">
-        <v>1863.4</v>
+        <v>1857.91</v>
       </c>
       <c r="E241" t="n">
         <v>1869.04</v>
       </c>
       <c r="F241" t="n">
-        <v>945417301</v>
+        <v>694888207</v>
       </c>
     </row>
     <row r="242">
@@ -5305,7 +5305,7 @@
         <v>1878.02</v>
       </c>
       <c r="F242" t="n">
-        <v>633056398</v>
+        <v>494031560</v>
       </c>
     </row>
     <row r="243">
@@ -5319,13 +5319,13 @@
         <v>1880.16</v>
       </c>
       <c r="D243" t="n">
-        <v>1854.08</v>
+        <v>1856.3</v>
       </c>
       <c r="E243" t="n">
         <v>1863.07</v>
       </c>
       <c r="F243" t="n">
-        <v>490618259</v>
+        <v>400816982</v>
       </c>
     </row>
     <row r="244">
@@ -5345,7 +5345,7 @@
         <v>1871.91</v>
       </c>
       <c r="F244" t="n">
-        <v>533612987</v>
+        <v>408688231</v>
       </c>
     </row>
     <row r="245">
@@ -5356,7 +5356,7 @@
         <v>1868.64</v>
       </c>
       <c r="C245" t="n">
-        <v>1869.52</v>
+        <v>1871.91</v>
       </c>
       <c r="D245" t="n">
         <v>1852.2</v>
@@ -5365,7 +5365,7 @@
         <v>1854.97</v>
       </c>
       <c r="F245" t="n">
-        <v>599912666</v>
+        <v>444788551</v>
       </c>
     </row>
     <row r="246">
@@ -5385,7 +5385,7 @@
         <v>1860.01</v>
       </c>
       <c r="F246" t="n">
-        <v>692765051</v>
+        <v>505116145</v>
       </c>
     </row>
     <row r="247">
@@ -5405,7 +5405,7 @@
         <v>1867.21</v>
       </c>
       <c r="F247" t="n">
-        <v>615059624</v>
+        <v>491315339</v>
       </c>
     </row>
     <row r="248">
@@ -5425,7 +5425,7 @@
         <v>1866.35</v>
       </c>
       <c r="F248" t="n">
-        <v>565120875</v>
+        <v>452764594</v>
       </c>
     </row>
     <row r="249">
@@ -5445,7 +5445,7 @@
         <v>1862.08</v>
       </c>
       <c r="F249" t="n">
-        <v>610754645</v>
+        <v>538080668</v>
       </c>
     </row>
     <row r="250">
@@ -5465,7 +5465,7 @@
         <v>1843.5</v>
       </c>
       <c r="F250" t="n">
-        <v>798795216</v>
+        <v>712579803</v>
       </c>
     </row>
     <row r="251">
@@ -5485,7 +5485,7 @@
         <v>1848.25</v>
       </c>
       <c r="F251" t="n">
-        <v>555740727</v>
+        <v>462997990</v>
       </c>
     </row>
     <row r="252">
@@ -5505,7 +5505,7 @@
         <v>1853.7</v>
       </c>
       <c r="F252" t="n">
-        <v>665008700</v>
+        <v>550621594</v>
       </c>
     </row>
     <row r="253">
@@ -5516,16 +5516,16 @@
         <v>1843.01</v>
       </c>
       <c r="C253" t="n">
-        <v>1850.56</v>
+        <v>1853.7</v>
       </c>
       <c r="D253" t="n">
-        <v>1838.26</v>
+        <v>1840.7</v>
       </c>
       <c r="E253" t="n">
         <v>1840.7</v>
       </c>
       <c r="F253" t="n">
-        <v>587308279</v>
+        <v>459418630</v>
       </c>
     </row>
     <row r="254">
@@ -5539,13 +5539,13 @@
         <v>1845.86</v>
       </c>
       <c r="D254" t="n">
-        <v>1827.5</v>
+        <v>1828.34</v>
       </c>
       <c r="E254" t="n">
         <v>1828.34</v>
       </c>
       <c r="F254" t="n">
-        <v>592728766</v>
+        <v>493196915</v>
       </c>
     </row>
     <row r="255">
@@ -5565,7 +5565,7 @@
         <v>1800.54</v>
       </c>
       <c r="F255" t="n">
-        <v>849625055</v>
+        <v>728451859</v>
       </c>
     </row>
     <row r="256">
@@ -5576,7 +5576,7 @@
         <v>1793.23</v>
       </c>
       <c r="C256" t="n">
-        <v>1806.63</v>
+        <v>1806.77</v>
       </c>
       <c r="D256" t="n">
         <v>1774.22</v>
@@ -5585,7 +5585,7 @@
         <v>1806.63</v>
       </c>
       <c r="F256" t="n">
-        <v>564797508</v>
+        <v>488594894</v>
       </c>
     </row>
     <row r="257">
@@ -5596,7 +5596,7 @@
         <v>1805.93</v>
       </c>
       <c r="C257" t="n">
-        <v>1805.93</v>
+        <v>1806.63</v>
       </c>
       <c r="D257" t="n">
         <v>1776.83</v>
@@ -5605,7 +5605,7 @@
         <v>1782.12</v>
       </c>
       <c r="F257" t="n">
-        <v>607367371</v>
+        <v>508398737</v>
       </c>
     </row>
     <row r="258">
@@ -5625,7 +5625,7 @@
         <v>1804.24</v>
       </c>
       <c r="F258" t="n">
-        <v>788701791</v>
+        <v>716663694</v>
       </c>
     </row>
     <row r="259">
@@ -5636,16 +5636,16 @@
         <v>1801.89</v>
       </c>
       <c r="C259" t="n">
-        <v>1803.14</v>
+        <v>1804.24</v>
       </c>
       <c r="D259" t="n">
-        <v>1780.3</v>
+        <v>1787.45</v>
       </c>
       <c r="E259" t="n">
         <v>1787.45</v>
       </c>
       <c r="F259" t="n">
-        <v>436669396</v>
+        <v>385810817</v>
       </c>
     </row>
     <row r="260">
@@ -5656,7 +5656,7 @@
         <v>1782.93</v>
       </c>
       <c r="C260" t="n">
-        <v>1783.83</v>
+        <v>1787.45</v>
       </c>
       <c r="D260" t="n">
         <v>1736.43</v>
@@ -5665,7 +5665,7 @@
         <v>1743.51</v>
       </c>
       <c r="F260" t="n">
-        <v>862568937</v>
+        <v>789163854</v>
       </c>
     </row>
     <row r="261">
@@ -5679,13 +5679,13 @@
         <v>1750.3</v>
       </c>
       <c r="D261" t="n">
-        <v>1722.55</v>
+        <v>1725.34</v>
       </c>
       <c r="E261" t="n">
         <v>1730.56</v>
       </c>
       <c r="F261" t="n">
-        <v>789069211</v>
+        <v>573145977</v>
       </c>
     </row>
     <row r="262">
@@ -5699,13 +5699,13 @@
         <v>1736.91</v>
       </c>
       <c r="D262" t="n">
-        <v>1666.43</v>
+        <v>1668.53</v>
       </c>
       <c r="E262" t="n">
         <v>1668.53</v>
       </c>
       <c r="F262" t="n">
-        <v>915046404</v>
+        <v>847743499</v>
       </c>
     </row>
     <row r="263">
@@ -5725,7 +5725,7 @@
         <v>1699.38</v>
       </c>
       <c r="F263" t="n">
-        <v>864451379</v>
+        <v>767199044</v>
       </c>
     </row>
     <row r="264">
@@ -5745,7 +5745,7 @@
         <v>1686.11</v>
       </c>
       <c r="F264" t="n">
-        <v>589610571</v>
+        <v>497795740</v>
       </c>
     </row>
     <row r="265">
@@ -5759,13 +5759,13 @@
         <v>1700.69</v>
       </c>
       <c r="D265" t="n">
-        <v>1667.66</v>
+        <v>1669.01</v>
       </c>
       <c r="E265" t="n">
         <v>1669.01</v>
       </c>
       <c r="F265" t="n">
-        <v>635422543</v>
+        <v>542734230</v>
       </c>
     </row>
     <row r="266">
@@ -5785,7 +5785,7 @@
         <v>1680.62</v>
       </c>
       <c r="F266" t="n">
-        <v>805989839</v>
+        <v>634234923</v>
       </c>
     </row>
     <row r="267">
@@ -5805,7 +5805,7 @@
         <v>1704.68</v>
       </c>
       <c r="F267" t="n">
-        <v>560537690</v>
+        <v>457457780</v>
       </c>
     </row>
     <row r="268">
@@ -5825,7 +5825,7 @@
         <v>1744.66</v>
       </c>
       <c r="F268" t="n">
-        <v>857446407</v>
+        <v>704381924</v>
       </c>
     </row>
     <row r="269">
@@ -5839,13 +5839,13 @@
         <v>1764.45</v>
       </c>
       <c r="D269" t="n">
-        <v>1708.61</v>
+        <v>1735.36</v>
       </c>
       <c r="E269" t="n">
         <v>1735.78</v>
       </c>
       <c r="F269" t="n">
-        <v>762488640</v>
+        <v>607287517</v>
       </c>
     </row>
     <row r="270">
@@ -5859,13 +5859,13 @@
         <v>1767.58</v>
       </c>
       <c r="D270" t="n">
-        <v>1737.26</v>
+        <v>1735.78</v>
       </c>
       <c r="E270" t="n">
         <v>1762.84</v>
       </c>
       <c r="F270" t="n">
-        <v>770849127</v>
+        <v>652314888</v>
       </c>
     </row>
     <row r="271">
@@ -5885,7 +5885,7 @@
         <v>1777.23</v>
       </c>
       <c r="F271" t="n">
-        <v>686936880</v>
+        <v>533722479</v>
       </c>
     </row>
     <row r="272">
@@ -5899,13 +5899,13 @@
         <v>1790.87</v>
       </c>
       <c r="D272" t="n">
-        <v>1769.44</v>
+        <v>1773.39</v>
       </c>
       <c r="E272" t="n">
         <v>1776.46</v>
       </c>
       <c r="F272" t="n">
-        <v>759304437</v>
+        <v>630678743</v>
       </c>
     </row>
     <row r="273">
@@ -5919,13 +5919,13 @@
         <v>1784.65</v>
       </c>
       <c r="D273" t="n">
-        <v>1762.34</v>
+        <v>1764.32</v>
       </c>
       <c r="E273" t="n">
         <v>1764.78</v>
       </c>
       <c r="F273" t="n">
-        <v>579915937</v>
+        <v>470876516</v>
       </c>
     </row>
     <row r="274">
@@ -5945,7 +5945,7 @@
         <v>1768.06</v>
       </c>
       <c r="F274" t="n">
-        <v>660590646</v>
+        <v>529722667</v>
       </c>
     </row>
     <row r="275">
@@ -5965,7 +5965,7 @@
         <v>1776.77</v>
       </c>
       <c r="F275" t="n">
-        <v>732713082</v>
+        <v>622931255</v>
       </c>
     </row>
     <row r="276">
@@ -5979,13 +5979,13 @@
         <v>1789.35</v>
       </c>
       <c r="D276" t="n">
-        <v>1766.4</v>
+        <v>1772.03</v>
       </c>
       <c r="E276" t="n">
         <v>1773.41</v>
       </c>
       <c r="F276" t="n">
-        <v>640887832</v>
+        <v>553915398</v>
       </c>
     </row>
     <row r="277">
@@ -6005,7 +6005,7 @@
         <v>1793.18</v>
       </c>
       <c r="F277" t="n">
-        <v>573008948</v>
+        <v>452560911</v>
       </c>
     </row>
     <row r="278">
@@ -6019,13 +6019,13 @@
         <v>1798.79</v>
       </c>
       <c r="D278" t="n">
-        <v>1762.96</v>
+        <v>1765.63</v>
       </c>
       <c r="E278" t="n">
         <v>1765.63</v>
       </c>
       <c r="F278" t="n">
-        <v>750529815</v>
+        <v>640346210</v>
       </c>
     </row>
     <row r="279">
@@ -6045,7 +6045,7 @@
         <v>1729.08</v>
       </c>
       <c r="F279" t="n">
-        <v>737513274</v>
+        <v>635802237</v>
       </c>
     </row>
     <row r="280">
@@ -6065,7 +6065,7 @@
         <v>1727.46</v>
       </c>
       <c r="F280" t="n">
-        <v>522025005</v>
+        <v>396771648</v>
       </c>
     </row>
     <row r="281">
@@ -6085,7 +6085,7 @@
         <v>1732.02</v>
       </c>
       <c r="F281" t="n">
-        <v>550472662</v>
+        <v>450739454</v>
       </c>
     </row>
     <row r="282">
@@ -6093,7 +6093,7 @@
         <v>46253</v>
       </c>
       <c r="B282" t="n">
-        <v>1732.02</v>
+        <v>1731.28</v>
       </c>
       <c r="C282" t="n">
         <v>1734.39</v>
@@ -6105,7 +6105,7 @@
         <v>1726.69</v>
       </c>
       <c r="F282" t="n">
-        <v>582684342</v>
+        <v>390828453</v>
       </c>
     </row>
     <row r="283">
@@ -6119,13 +6119,13 @@
         <v>1742.38</v>
       </c>
       <c r="D283" t="n">
-        <v>1729.48</v>
+        <v>1726.69</v>
       </c>
       <c r="E283" t="n">
         <v>1734.24</v>
       </c>
       <c r="F283" t="n">
-        <v>464412231</v>
+        <v>339514782</v>
       </c>
     </row>
     <row r="284">
@@ -6145,7 +6145,7 @@
         <v>1768.12</v>
       </c>
       <c r="F284" t="n">
-        <v>783548119</v>
+        <v>667783227</v>
       </c>
     </row>
     <row r="285">
@@ -6159,13 +6159,13 @@
         <v>1795.38</v>
       </c>
       <c r="D285" t="n">
-        <v>1778.4</v>
+        <v>1768.12</v>
       </c>
       <c r="E285" t="n">
         <v>1788.78</v>
       </c>
       <c r="F285" t="n">
-        <v>880154054</v>
+        <v>669160018</v>
       </c>
     </row>
     <row r="286">
@@ -6185,7 +6185,7 @@
         <v>1791.41</v>
       </c>
       <c r="F286" t="n">
-        <v>839735691</v>
+        <v>643465330</v>
       </c>
     </row>
     <row r="287">
@@ -6205,7 +6205,7 @@
         <v>1821.32</v>
       </c>
       <c r="F287" t="n">
-        <v>731185942</v>
+        <v>587417275</v>
       </c>
     </row>
     <row r="288">
@@ -6225,7 +6225,7 @@
         <v>1831.56</v>
       </c>
       <c r="F288" t="n">
-        <v>610848504</v>
+        <v>484230398</v>
       </c>
     </row>
     <row r="289">
@@ -6245,7 +6245,7 @@
         <v>1832.12</v>
       </c>
       <c r="F289" t="n">
-        <v>643935725</v>
+        <v>562184482</v>
       </c>
     </row>
     <row r="290">
@@ -6325,7 +6325,7 @@
         <v>1827.72</v>
       </c>
       <c r="F293" t="n">
-        <v>633349761</v>
+        <v>520015604</v>
       </c>
     </row>
     <row r="294">
@@ -6345,7 +6345,7 @@
         <v>1853.08</v>
       </c>
       <c r="F294" t="n">
-        <v>618685672</v>
+        <v>500988851</v>
       </c>
     </row>
     <row r="295">
@@ -6365,7 +6365,7 @@
         <v>1821.64</v>
       </c>
       <c r="F295" t="n">
-        <v>643819662</v>
+        <v>498044335</v>
       </c>
     </row>
     <row r="296">
@@ -6385,7 +6385,7 @@
         <v>1830.44</v>
       </c>
       <c r="F296" t="n">
-        <v>559481540</v>
+        <v>403071199</v>
       </c>
     </row>
     <row r="297">
@@ -6405,7 +6405,7 @@
         <v>1827.12</v>
       </c>
       <c r="F297" t="n">
-        <v>566830089</v>
+        <v>467328995</v>
       </c>
     </row>
     <row r="298">
@@ -6425,7 +6425,7 @@
         <v>1829.23</v>
       </c>
       <c r="F298" t="n">
-        <v>484570078</v>
+        <v>383185655</v>
       </c>
     </row>
     <row r="299">
@@ -6436,7 +6436,7 @@
         <v>1820.11</v>
       </c>
       <c r="C299" t="n">
-        <v>1822.44</v>
+        <v>1829.23</v>
       </c>
       <c r="D299" t="n">
         <v>1795.21</v>
@@ -6445,7 +6445,7 @@
         <v>1795.21</v>
       </c>
       <c r="F299" t="n">
-        <v>697692122</v>
+        <v>628257109</v>
       </c>
     </row>
     <row r="300">
@@ -6465,7 +6465,7 @@
         <v>1788.23</v>
       </c>
       <c r="F300" t="n">
-        <v>823996368</v>
+        <v>663718670</v>
       </c>
     </row>
     <row r="301">
@@ -6479,13 +6479,13 @@
         <v>1812.07</v>
       </c>
       <c r="D301" t="n">
-        <v>1794.76</v>
+        <v>1788.23</v>
       </c>
       <c r="E301" t="n">
         <v>1811.15</v>
       </c>
       <c r="F301" t="n">
-        <v>642481052</v>
+        <v>523818299</v>
       </c>
     </row>
     <row r="302">
@@ -6505,7 +6505,27 @@
         <v>1810.11</v>
       </c>
       <c r="F302" t="n">
-        <v>592811094</v>
+        <v>446938604</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1805.15</v>
+      </c>
+      <c r="C303" t="n">
+        <v>1830.35</v>
+      </c>
+      <c r="D303" t="n">
+        <v>1794.49</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1822.77</v>
+      </c>
+      <c r="F303" t="n">
+        <v>720906040</v>
       </c>
     </row>
   </sheetData>
